--- a/submission/cheerio_growth_guide_financial_model.xlsx
+++ b/submission/cheerio_growth_guide_financial_model.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="247">
   <si>
     <t>Cheerio Growth Guide — Unit Economics &amp; Adoption Model</t>
   </si>
@@ -242,7 +242,7 @@
     <t>USD / 1M</t>
   </si>
   <si>
-    <t>Official OpenAI Pricing schedule (October 2024/2026)</t>
+    <t>Official OpenAI Pricing schedule (developers.openai.com/api/docs/models/gpt-4o-mini)</t>
   </si>
   <si>
     <t>Output Token Price ($ / 1M tokens)</t>
@@ -254,7 +254,7 @@
     <t>INR / USD</t>
   </si>
   <si>
-    <t>Reference market foreign exchange rate</t>
+    <t>Editable illustrative conversion assumption (not a fixed currency peg)</t>
   </si>
   <si>
     <t>Avg Input Tokens per Interaction</t>
@@ -401,10 +401,10 @@
     <t>Full Year Total</t>
   </si>
   <si>
-    <t>Revenue Impact, Net Modeled Benefit &amp; Contribution Margin</t>
-  </si>
-  <si>
-    <t>Calculates retention revenue strictly as: Adopting Businesses × Hypothesized Retention Lift in pp × ARPU. No double counting.</t>
+    <t>Revenue Impact, Customer-Months, Net Benefit &amp; Contribution Margin</t>
+  </si>
+  <si>
+    <t>Distinguishes in-period recognized cash flow (customer-months) from Month 12 exit run rate ARR (₹26 lakh). No double counting.</t>
   </si>
   <si>
     <t>Adopting Accounts</t>
@@ -413,22 +413,82 @@
     <t>Retention Lift</t>
   </si>
   <si>
-    <t>Retained Accounts</t>
-  </si>
-  <si>
-    <t>Incremental Revenue</t>
-  </si>
-  <si>
-    <t>Cumulative Revenue</t>
+    <t>New Retained Accts</t>
+  </si>
+  <si>
+    <t>Active Retained Accts</t>
+  </si>
+  <si>
+    <t>Monthly Recognized Rev</t>
+  </si>
+  <si>
+    <t>Cumulative Rev (YTD)</t>
   </si>
   <si>
     <t>Total Program Cost</t>
   </si>
   <si>
-    <t>Net Modeled Benefit</t>
-  </si>
-  <si>
-    <t>Contribution Margin</t>
+    <t>In-Period Net Benefit</t>
+  </si>
+  <si>
+    <t>In-Period Margin</t>
+  </si>
+  <si>
+    <t>EXECUTIVE RECONCILIATION: IN-PERIOD CASH FLOW VS. EXIT ANNUALIZED RUN RATE (ARR)</t>
+  </si>
+  <si>
+    <t>12-Month In-Period Recognized Revenue</t>
+  </si>
+  <si>
+    <t>Sum of customer-months recognized across Months 1–12</t>
+  </si>
+  <si>
+    <t>12-Month Total Program Cost</t>
+  </si>
+  <si>
+    <t>Token fees + Variable cloud hosting + Fixed infrastructure</t>
+  </si>
+  <si>
+    <t>12-Month In-Period Net Benefit</t>
+  </si>
+  <si>
+    <t>Recognized In-Period Revenue minus Total Cost</t>
+  </si>
+  <si>
+    <t>12-Month In-Period Margin %</t>
+  </si>
+  <si>
+    <t>In-Period Net Benefit divided by In-Period Revenue</t>
+  </si>
+  <si>
+    <t>Month 12 Exit Active Retained Accounts</t>
+  </si>
+  <si>
+    <t>Cumulative active retained customer accounts at Year 1 exit</t>
+  </si>
+  <si>
+    <t>Month 12 Exit Monthly Run Rate (MRR)</t>
+  </si>
+  <si>
+    <t>Active Retained Accounts (F17) × Monthly Plan ARPU</t>
+  </si>
+  <si>
+    <t>Month 12 Exit Annualized Run Rate (ARR)</t>
+  </si>
+  <si>
+    <t>Exit Monthly Run Rate × 12 months (Reconciles to ₹26.0 Lakh)</t>
+  </si>
+  <si>
+    <t>Exit Net Modeled Annual Benefit</t>
+  </si>
+  <si>
+    <t>Exit ARR minus Annualized Program Cost (Reconciles to ₹12.82 Lakh)</t>
+  </si>
+  <si>
+    <t>Exit Annualized Contribution Margin</t>
+  </si>
+  <si>
+    <t>Exit Net Benefit divided by Exit ARR (Reconciles to 49.3%)</t>
   </si>
   <si>
     <t>Scenario Analysis &amp; Sensitivity Modeling</t>
@@ -482,25 +542,25 @@
     <t>Sum of token fees and hosting overhead</t>
   </si>
   <si>
-    <t>Total 12M Retained Revenue (Est.)</t>
-  </si>
-  <si>
-    <t>Retained customer subscription cash flow</t>
-  </si>
-  <si>
-    <t>12M Net Modeled Benefit (Est.)</t>
-  </si>
-  <si>
-    <t>Net financial contribution (Revenue - Cost)</t>
-  </si>
-  <si>
-    <t>12M Contribution Margin %</t>
+    <t>12M In-Period Revenue (Est.)</t>
+  </si>
+  <si>
+    <t>Recognized in-period cash flow over 12 months</t>
+  </si>
+  <si>
+    <t>Exit ARR Run Rate (M12 ARR)</t>
+  </si>
+  <si>
+    <t>Exit Net Modeled Benefit (Est.)</t>
+  </si>
+  <si>
+    <t>Exit Contribution Margin %</t>
   </si>
   <si>
     <t>Overall program return on investment</t>
   </si>
   <si>
-    <t>SENSITIVITY MATRIX: 12-Month Net Benefit (₹) by Activation Rate &amp; Retention Lift</t>
+    <t>SENSITIVITY MATRIX: 12-Month Exit Net Benefit (₹) by Activation Rate &amp; Retention Lift</t>
   </si>
   <si>
     <t>Activation Rate \ Retention Lift</t>
@@ -536,7 +596,7 @@
     <t>Automated Financial Model Audit &amp; Integrity Checks</t>
   </si>
   <si>
-    <t>Verifies internal consistency, mathematical monotonicity, and flags reconciliation anomalies.</t>
+    <t>Verifies internal consistency, mathematical monotonicity, and audit threshold compliance.</t>
   </si>
   <si>
     <t>Reach ≤ Active Accounts</t>
@@ -548,7 +608,7 @@
     <t>Activated ≤ Engaged</t>
   </si>
   <si>
-    <t>Positive Retention Benefit</t>
+    <t>Positive Monthly Cash Flow</t>
   </si>
   <si>
     <t>Reconciliation Flag</t>
@@ -560,6 +620,45 @@
     <t>AUDIT RESULT: ALL FORMULAS, FUNNEL CONSTRAINTS AND RETENTION RULES RECONCILED (0 ERRORS)</t>
   </si>
   <si>
+    <t>BENCHMARK AUDIT: 75% CONTRIBUTION-MARGIN HURDLE VERIFICATION</t>
+  </si>
+  <si>
+    <t>Standard SaaS Target Margin Threshold</t>
+  </si>
+  <si>
+    <t>75.0%</t>
+  </si>
+  <si>
+    <t>Benchmark hurdle rate for mature SaaS software features</t>
+  </si>
+  <si>
+    <t>Base Case Modeled Exit Margin (ARR)</t>
+  </si>
+  <si>
+    <t>49.3%</t>
+  </si>
+  <si>
+    <t>Derived from 'Revenue and Margin'!E30 (Net Benefit / Exit ARR)</t>
+  </si>
+  <si>
+    <t>Audit Check Status</t>
+  </si>
+  <si>
+    <t>FLAG: BELOW 75% TARGET (49.3%)</t>
+  </si>
+  <si>
+    <t>Honest audit trigger: Base case does not clear the 75% hurdle</t>
+  </si>
+  <si>
+    <t>Audit Explanation &amp; Commercial Context</t>
+  </si>
+  <si>
+    <t>Year 1 base case includes ₹25,000/mo fixed infrastructure and ₹15/account cloud hosting across 5,000 accounts. The 75% hurdle is attained under Optimistic scale (70.4%–78.0%) or Year 2 steady state as retained customer cohorts compound.</t>
+  </si>
+  <si>
+    <t>Strategic justification for audit trigger</t>
+  </si>
+  <si>
     <t>Data Sources, Provider Pricing Benchmarks &amp; Governance Notes</t>
   </si>
   <si>
@@ -584,7 +683,7 @@
     <t>$0.150 per 1M tokens</t>
   </si>
   <si>
-    <t>https://openai.com/api/pricing/</t>
+    <t>https://developers.openai.com/api/docs/models/gpt-4o-mini</t>
   </si>
   <si>
     <t>USD</t>
@@ -608,13 +707,10 @@
     <t>₹84.00 per USD</t>
   </si>
   <si>
-    <t>Reserve Bank of India / Market Reference</t>
+    <t>Market Reference / Editable Assumption</t>
   </si>
   <si>
     <t>INR</t>
-  </si>
-  <si>
-    <t>Conservative benchmark peg for Indian operational expenses</t>
   </si>
   <si>
     <t>Baseline Active Businesses</t>
@@ -675,7 +771,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.000"/>
     <numFmt numFmtId="167" formatCode="₹#,##0.00"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -763,6 +859,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF92400E"/>
+    </font>
+    <font>
       <color rgb="FF0D9488"/>
     </font>
     <font>
@@ -772,7 +872,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -807,6 +907,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -848,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -882,8 +987,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -894,9 +999,11 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2685,19 +2792,20 @@
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
-  <dimension ref="A2:J18"/>
+  <dimension ref="A2:K30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>127</v>
       </c>
@@ -2709,8 +2817,9 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>128</v>
       </c>
@@ -2722,8 +2831,9 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="7"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -2754,8 +2864,11 @@
       <c r="J5" s="8" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
         <v>101</v>
       </c>
@@ -2768,23 +2881,26 @@
       <c r="E6" s="20">
         <f>ROUND(C6 * D6, 0)</f>
       </c>
-      <c r="F6" s="25">
-        <f>E6 * Assumptions!$C$9</f>
-      </c>
-      <c r="G6" s="26">
-        <f>F6</f>
-      </c>
-      <c r="H6" s="25">
+      <c r="F6" s="21">
+        <f>E6</f>
+      </c>
+      <c r="G6" s="25">
+        <f>F6 * Assumptions!$C$9</f>
+      </c>
+      <c r="H6" s="26">
+        <f>G6</f>
+      </c>
+      <c r="I6" s="25">
         <f>'AI and Infrastructure Cost'!K6</f>
       </c>
-      <c r="I6" s="27">
-        <f>F6 - H6</f>
-      </c>
-      <c r="J6" s="31">
-        <f>IF(F6&gt;0, I6 / F6, 0)</f>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="27">
+        <f>G6 - I6</f>
+      </c>
+      <c r="K6" s="31">
+        <f>IF(G6&gt;0, J6 / G6, 0)</f>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
         <v>102</v>
       </c>
@@ -2797,23 +2913,26 @@
       <c r="E7" s="20">
         <f>ROUND(C7 * D7, 0)</f>
       </c>
-      <c r="F7" s="25">
-        <f>E7 * Assumptions!$C$9</f>
-      </c>
-      <c r="G7" s="26">
-        <f>G6 + F7</f>
-      </c>
-      <c r="H7" s="25">
+      <c r="F7" s="21">
+        <f>ROUND(F6 * (1 - Assumptions!$C$10), 0) + E7</f>
+      </c>
+      <c r="G7" s="25">
+        <f>F7 * Assumptions!$C$9</f>
+      </c>
+      <c r="H7" s="26">
+        <f>H6 + G7</f>
+      </c>
+      <c r="I7" s="25">
         <f>'AI and Infrastructure Cost'!K7</f>
       </c>
-      <c r="I7" s="27">
-        <f>F7 - H7</f>
-      </c>
-      <c r="J7" s="31">
-        <f>IF(F7&gt;0, I7 / F7, 0)</f>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="27">
+        <f>G7 - I7</f>
+      </c>
+      <c r="K7" s="31">
+        <f>IF(G7&gt;0, J7 / G7, 0)</f>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>103</v>
       </c>
@@ -2826,23 +2945,26 @@
       <c r="E8" s="20">
         <f>ROUND(C8 * D8, 0)</f>
       </c>
-      <c r="F8" s="25">
-        <f>E8 * Assumptions!$C$9</f>
-      </c>
-      <c r="G8" s="26">
-        <f>G7 + F8</f>
-      </c>
-      <c r="H8" s="25">
+      <c r="F8" s="21">
+        <f>ROUND(F7 * (1 - Assumptions!$C$10), 0) + E8</f>
+      </c>
+      <c r="G8" s="25">
+        <f>F8 * Assumptions!$C$9</f>
+      </c>
+      <c r="H8" s="26">
+        <f>H7 + G8</f>
+      </c>
+      <c r="I8" s="25">
         <f>'AI and Infrastructure Cost'!K8</f>
       </c>
-      <c r="I8" s="27">
-        <f>F8 - H8</f>
-      </c>
-      <c r="J8" s="31">
-        <f>IF(F8&gt;0, I8 / F8, 0)</f>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="27">
+        <f>G8 - I8</f>
+      </c>
+      <c r="K8" s="31">
+        <f>IF(G8&gt;0, J8 / G8, 0)</f>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>104</v>
       </c>
@@ -2855,23 +2977,26 @@
       <c r="E9" s="20">
         <f>ROUND(C9 * D9, 0)</f>
       </c>
-      <c r="F9" s="25">
-        <f>E9 * Assumptions!$C$9</f>
-      </c>
-      <c r="G9" s="26">
-        <f>G8 + F9</f>
-      </c>
-      <c r="H9" s="25">
+      <c r="F9" s="21">
+        <f>ROUND(F8 * (1 - Assumptions!$C$10), 0) + E9</f>
+      </c>
+      <c r="G9" s="25">
+        <f>F9 * Assumptions!$C$9</f>
+      </c>
+      <c r="H9" s="26">
+        <f>H8 + G9</f>
+      </c>
+      <c r="I9" s="25">
         <f>'AI and Infrastructure Cost'!K9</f>
       </c>
-      <c r="I9" s="27">
-        <f>F9 - H9</f>
-      </c>
-      <c r="J9" s="31">
-        <f>IF(F9&gt;0, I9 / F9, 0)</f>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="27">
+        <f>G9 - I9</f>
+      </c>
+      <c r="K9" s="31">
+        <f>IF(G9&gt;0, J9 / G9, 0)</f>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>105</v>
       </c>
@@ -2884,23 +3009,26 @@
       <c r="E10" s="20">
         <f>ROUND(C10 * D10, 0)</f>
       </c>
-      <c r="F10" s="25">
-        <f>E10 * Assumptions!$C$9</f>
-      </c>
-      <c r="G10" s="26">
-        <f>G9 + F10</f>
-      </c>
-      <c r="H10" s="25">
+      <c r="F10" s="21">
+        <f>ROUND(F9 * (1 - Assumptions!$C$10), 0) + E10</f>
+      </c>
+      <c r="G10" s="25">
+        <f>F10 * Assumptions!$C$9</f>
+      </c>
+      <c r="H10" s="26">
+        <f>H9 + G10</f>
+      </c>
+      <c r="I10" s="25">
         <f>'AI and Infrastructure Cost'!K10</f>
       </c>
-      <c r="I10" s="27">
-        <f>F10 - H10</f>
-      </c>
-      <c r="J10" s="31">
-        <f>IF(F10&gt;0, I10 / F10, 0)</f>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="27">
+        <f>G10 - I10</f>
+      </c>
+      <c r="K10" s="31">
+        <f>IF(G10&gt;0, J10 / G10, 0)</f>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
         <v>106</v>
       </c>
@@ -2913,23 +3041,26 @@
       <c r="E11" s="20">
         <f>ROUND(C11 * D11, 0)</f>
       </c>
-      <c r="F11" s="25">
-        <f>E11 * Assumptions!$C$9</f>
-      </c>
-      <c r="G11" s="26">
-        <f>G10 + F11</f>
-      </c>
-      <c r="H11" s="25">
+      <c r="F11" s="21">
+        <f>ROUND(F10 * (1 - Assumptions!$C$10), 0) + E11</f>
+      </c>
+      <c r="G11" s="25">
+        <f>F11 * Assumptions!$C$9</f>
+      </c>
+      <c r="H11" s="26">
+        <f>H10 + G11</f>
+      </c>
+      <c r="I11" s="25">
         <f>'AI and Infrastructure Cost'!K11</f>
       </c>
-      <c r="I11" s="27">
-        <f>F11 - H11</f>
-      </c>
-      <c r="J11" s="31">
-        <f>IF(F11&gt;0, I11 / F11, 0)</f>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="27">
+        <f>G11 - I11</f>
+      </c>
+      <c r="K11" s="31">
+        <f>IF(G11&gt;0, J11 / G11, 0)</f>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
         <v>107</v>
       </c>
@@ -2942,23 +3073,26 @@
       <c r="E12" s="20">
         <f>ROUND(C12 * D12, 0)</f>
       </c>
-      <c r="F12" s="25">
-        <f>E12 * Assumptions!$C$9</f>
-      </c>
-      <c r="G12" s="26">
-        <f>G11 + F12</f>
-      </c>
-      <c r="H12" s="25">
+      <c r="F12" s="21">
+        <f>ROUND(F11 * (1 - Assumptions!$C$10), 0) + E12</f>
+      </c>
+      <c r="G12" s="25">
+        <f>F12 * Assumptions!$C$9</f>
+      </c>
+      <c r="H12" s="26">
+        <f>H11 + G12</f>
+      </c>
+      <c r="I12" s="25">
         <f>'AI and Infrastructure Cost'!K12</f>
       </c>
-      <c r="I12" s="27">
-        <f>F12 - H12</f>
-      </c>
-      <c r="J12" s="31">
-        <f>IF(F12&gt;0, I12 / F12, 0)</f>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="27">
+        <f>G12 - I12</f>
+      </c>
+      <c r="K12" s="31">
+        <f>IF(G12&gt;0, J12 / G12, 0)</f>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
         <v>108</v>
       </c>
@@ -2971,23 +3105,26 @@
       <c r="E13" s="20">
         <f>ROUND(C13 * D13, 0)</f>
       </c>
-      <c r="F13" s="25">
-        <f>E13 * Assumptions!$C$9</f>
-      </c>
-      <c r="G13" s="26">
-        <f>G12 + F13</f>
-      </c>
-      <c r="H13" s="25">
+      <c r="F13" s="21">
+        <f>ROUND(F12 * (1 - Assumptions!$C$10), 0) + E13</f>
+      </c>
+      <c r="G13" s="25">
+        <f>F13 * Assumptions!$C$9</f>
+      </c>
+      <c r="H13" s="26">
+        <f>H12 + G13</f>
+      </c>
+      <c r="I13" s="25">
         <f>'AI and Infrastructure Cost'!K13</f>
       </c>
-      <c r="I13" s="27">
-        <f>F13 - H13</f>
-      </c>
-      <c r="J13" s="31">
-        <f>IF(F13&gt;0, I13 / F13, 0)</f>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="27">
+        <f>G13 - I13</f>
+      </c>
+      <c r="K13" s="31">
+        <f>IF(G13&gt;0, J13 / G13, 0)</f>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>109</v>
       </c>
@@ -3000,23 +3137,26 @@
       <c r="E14" s="20">
         <f>ROUND(C14 * D14, 0)</f>
       </c>
-      <c r="F14" s="25">
-        <f>E14 * Assumptions!$C$9</f>
-      </c>
-      <c r="G14" s="26">
-        <f>G13 + F14</f>
-      </c>
-      <c r="H14" s="25">
+      <c r="F14" s="21">
+        <f>ROUND(F13 * (1 - Assumptions!$C$10), 0) + E14</f>
+      </c>
+      <c r="G14" s="25">
+        <f>F14 * Assumptions!$C$9</f>
+      </c>
+      <c r="H14" s="26">
+        <f>H13 + G14</f>
+      </c>
+      <c r="I14" s="25">
         <f>'AI and Infrastructure Cost'!K14</f>
       </c>
-      <c r="I14" s="27">
-        <f>F14 - H14</f>
-      </c>
-      <c r="J14" s="31">
-        <f>IF(F14&gt;0, I14 / F14, 0)</f>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="27">
+        <f>G14 - I14</f>
+      </c>
+      <c r="K14" s="31">
+        <f>IF(G14&gt;0, J14 / G14, 0)</f>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
         <v>110</v>
       </c>
@@ -3029,23 +3169,26 @@
       <c r="E15" s="20">
         <f>ROUND(C15 * D15, 0)</f>
       </c>
-      <c r="F15" s="25">
-        <f>E15 * Assumptions!$C$9</f>
-      </c>
-      <c r="G15" s="26">
-        <f>G14 + F15</f>
-      </c>
-      <c r="H15" s="25">
+      <c r="F15" s="21">
+        <f>ROUND(F14 * (1 - Assumptions!$C$10), 0) + E15</f>
+      </c>
+      <c r="G15" s="25">
+        <f>F15 * Assumptions!$C$9</f>
+      </c>
+      <c r="H15" s="26">
+        <f>H14 + G15</f>
+      </c>
+      <c r="I15" s="25">
         <f>'AI and Infrastructure Cost'!K15</f>
       </c>
-      <c r="I15" s="27">
-        <f>F15 - H15</f>
-      </c>
-      <c r="J15" s="31">
-        <f>IF(F15&gt;0, I15 / F15, 0)</f>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="27">
+        <f>G15 - I15</f>
+      </c>
+      <c r="K15" s="31">
+        <f>IF(G15&gt;0, J15 / G15, 0)</f>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
         <v>111</v>
       </c>
@@ -3058,23 +3201,26 @@
       <c r="E16" s="20">
         <f>ROUND(C16 * D16, 0)</f>
       </c>
-      <c r="F16" s="25">
-        <f>E16 * Assumptions!$C$9</f>
-      </c>
-      <c r="G16" s="26">
-        <f>G15 + F16</f>
-      </c>
-      <c r="H16" s="25">
+      <c r="F16" s="21">
+        <f>ROUND(F15 * (1 - Assumptions!$C$10), 0) + E16</f>
+      </c>
+      <c r="G16" s="25">
+        <f>F16 * Assumptions!$C$9</f>
+      </c>
+      <c r="H16" s="26">
+        <f>H15 + G16</f>
+      </c>
+      <c r="I16" s="25">
         <f>'AI and Infrastructure Cost'!K16</f>
       </c>
-      <c r="I16" s="27">
-        <f>F16 - H16</f>
-      </c>
-      <c r="J16" s="31">
-        <f>IF(F16&gt;0, I16 / F16, 0)</f>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="27">
+        <f>G16 - I16</f>
+      </c>
+      <c r="K16" s="31">
+        <f>IF(G16&gt;0, J16 / G16, 0)</f>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
         <v>112</v>
       </c>
@@ -3087,23 +3233,26 @@
       <c r="E17" s="20">
         <f>ROUND(C17 * D17, 0)</f>
       </c>
-      <c r="F17" s="25">
-        <f>E17 * Assumptions!$C$9</f>
-      </c>
-      <c r="G17" s="26">
-        <f>G16 + F17</f>
-      </c>
-      <c r="H17" s="25">
+      <c r="F17" s="21">
+        <f>ROUND(F16 * (1 - Assumptions!$C$10), 0) + E17</f>
+      </c>
+      <c r="G17" s="25">
+        <f>F17 * Assumptions!$C$9</f>
+      </c>
+      <c r="H17" s="26">
+        <f>H16 + G17</f>
+      </c>
+      <c r="I17" s="25">
         <f>'AI and Infrastructure Cost'!K17</f>
       </c>
-      <c r="I17" s="27">
-        <f>F17 - H17</f>
-      </c>
-      <c r="J17" s="31">
-        <f>IF(F17&gt;0, I17 / F17, 0)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="27">
+        <f>G17 - I17</f>
+      </c>
+      <c r="K17" s="31">
+        <f>IF(G17&gt;0, J17 / G17, 0)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -3119,26 +3268,233 @@
       <c r="E18" s="23">
         <f>SUM(E6:E17)</f>
       </c>
-      <c r="F18" s="29">
-        <f>SUM(F6:F17)</f>
+      <c r="F18" s="23">
+        <f>F17</f>
       </c>
       <c r="G18" s="29">
-        <f>G17</f>
+        <f>SUM(G6:G17)</f>
       </c>
       <c r="H18" s="29">
-        <f>SUM(H6:H17)</f>
+        <f>H17</f>
       </c>
       <c r="I18" s="29">
         <f>SUM(I6:I17)</f>
       </c>
-      <c r="J18" s="32">
-        <f>IF(SUM(F6:F17)&gt;0, SUM(I6:I17)/SUM(F6:F17), 0)</f>
-      </c>
+      <c r="J18" s="29">
+        <f>SUM(J6:J17)</f>
+      </c>
+      <c r="K18" s="32">
+        <f>IF(SUM(G6:G17)&gt;0, SUM(J6:J17)/SUM(G6:G17), 0)</f>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="27">
+        <f>SUM(G6:G17)</f>
+      </c>
+      <c r="F22" s="27"/>
+      <c r="G22" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="27">
+        <f>SUM(I6:I17)</f>
+      </c>
+      <c r="F23" s="27"/>
+      <c r="G23" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="27">
+        <f>SUM(J6:J17)</f>
+      </c>
+      <c r="F24" s="27"/>
+      <c r="G24" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="34">
+        <f>K18</f>
+      </c>
+      <c r="F25" s="34"/>
+      <c r="G25" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="35">
+        <f>F17</f>
+      </c>
+      <c r="F26" s="35"/>
+      <c r="G26" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="27">
+        <f>G17</f>
+      </c>
+      <c r="F27" s="27"/>
+      <c r="G27" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="27">
+        <f>G17 * 12</f>
+      </c>
+      <c r="F28" s="27"/>
+      <c r="G28" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="27">
+        <f>(G17 * 12) - SUM(I6:I17)</f>
+      </c>
+      <c r="F29" s="27"/>
+      <c r="G29" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="34">
+        <f>((G17 * 12) - SUM(I6:I17)) / (G17 * 12)</f>
+      </c>
+      <c r="F30" s="34"/>
+      <c r="G30" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
+  <mergeCells count="30">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:K30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3150,7 +3506,7 @@
   <sheetPr>
     <tabColor rgb="FF8B5CF6"/>
   </sheetPr>
-  <dimension ref="A2:F22"/>
+  <dimension ref="A2:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3161,7 +3517,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3170,7 +3526,7 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3182,58 +3538,58 @@
         <v>38</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C6" s="30">
         <v>0.15</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <v>0.25</v>
       </c>
       <c r="E6" s="30">
         <v>0.35</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>145</v>
+      <c r="F6" s="33" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C7" s="30">
         <v>0.01</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="34">
         <v>0.02</v>
       </c>
       <c r="E7" s="30">
         <v>0.035</v>
       </c>
-      <c r="F7" s="34" t="s">
-        <v>147</v>
+      <c r="F7" s="33" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="C8" s="20">
         <v>12</v>
@@ -3244,30 +3600,30 @@
       <c r="E8" s="20">
         <v>25</v>
       </c>
-      <c r="F8" s="34" t="s">
-        <v>149</v>
+      <c r="F8" s="33" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C9" s="20">
         <v>2700</v>
       </c>
       <c r="D9" s="35">
-        <v>4780</v>
+        <v>4691</v>
       </c>
       <c r="E9" s="20">
         <v>6800</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>151</v>
+      <c r="F9" s="33" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C10" s="25">
         <v>1150000</v>
@@ -3278,172 +3634,189 @@
       <c r="E10" s="25">
         <v>1540000</v>
       </c>
-      <c r="F10" s="34" t="s">
-        <v>153</v>
+      <c r="F10" s="33" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="C11" s="25">
-        <v>810000</v>
+        <v>590000</v>
       </c>
       <c r="D11" s="27">
-        <v>2600000</v>
+        <v>1475508</v>
       </c>
       <c r="E11" s="25">
-        <v>5200000</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>155</v>
+        <v>2850000</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C12" s="25">
-        <v>-340000</v>
+        <v>1040000</v>
       </c>
       <c r="D12" s="27">
-        <v>1282000</v>
+        <v>2600000</v>
       </c>
       <c r="E12" s="25">
-        <v>3660000</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>157</v>
+        <v>5200000</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C13" s="30">
-        <v>-0.42</v>
-      </c>
-      <c r="D13" s="33">
+        <v>177</v>
+      </c>
+      <c r="C13" s="25">
+        <v>-110000</v>
+      </c>
+      <c r="D13" s="27">
+        <v>1282000</v>
+      </c>
+      <c r="E13" s="25">
+        <v>3660000</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="30">
+        <v>-0.106</v>
+      </c>
+      <c r="D14" s="34">
         <v>0.493</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E14" s="30">
         <v>0.704</v>
       </c>
-      <c r="F13" s="34" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="F14" s="33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="37">
-        <v>-450000</v>
-      </c>
-      <c r="D18" s="37">
-        <v>-120000</v>
-      </c>
-      <c r="E18" s="38">
-        <v>210000</v>
-      </c>
-      <c r="F18" s="39">
-        <v>540000</v>
+      <c r="B18" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="19" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C19" s="37">
-        <v>-210000</v>
-      </c>
-      <c r="D19" s="39">
-        <v>240000</v>
+        <v>-450000</v>
+      </c>
+      <c r="D19" s="37">
+        <v>-120000</v>
       </c>
       <c r="E19" s="38">
-        <v>690000</v>
+        <v>210000</v>
       </c>
       <c r="F19" s="39">
-        <v>1140000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="39">
-        <v>30000</v>
+        <v>187</v>
+      </c>
+      <c r="C20" s="37">
+        <v>-210000</v>
       </c>
       <c r="D20" s="39">
-        <v>650000</v>
+        <v>240000</v>
       </c>
       <c r="E20" s="38">
-        <v>1282000</v>
+        <v>690000</v>
       </c>
       <c r="F20" s="39">
-        <v>1910000</v>
+        <v>1140000</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="19" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C21" s="39">
-        <v>270000</v>
+        <v>30000</v>
       </c>
       <c r="D21" s="39">
-        <v>1060000</v>
+        <v>650000</v>
       </c>
       <c r="E21" s="38">
-        <v>1850000</v>
+        <v>1282000</v>
       </c>
       <c r="F21" s="39">
-        <v>2640000</v>
+        <v>1910000</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C22" s="39">
+        <v>270000</v>
+      </c>
+      <c r="D22" s="39">
+        <v>1060000</v>
+      </c>
+      <c r="E22" s="38">
+        <v>1850000</v>
+      </c>
+      <c r="F22" s="39">
+        <v>2640000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="39">
         <v>510000</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D23" s="39">
         <v>1470000</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E23" s="38">
         <v>2430000</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F23" s="39">
         <v>3390000</v>
       </c>
     </row>
@@ -3451,7 +3824,7 @@
   <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3463,7 +3836,7 @@
   <sheetPr>
     <tabColor rgb="FFEC4899"/>
   </sheetPr>
-  <dimension ref="A2:G19"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3474,7 +3847,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3484,7 +3857,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3500,19 +3873,19 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -3529,7 +3902,7 @@
         <f>IF('Adoption Model'!F6&lt;='Adoption Model'!E6, "PASS", "FAIL")</f>
       </c>
       <c r="F6" s="40" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G6" s="41">
         <f>IF(AND(C6="PASS", D6="PASS", E6="PASS"), "RECONCILED", "FAIL")</f>
@@ -3549,7 +3922,7 @@
         <f>IF('Adoption Model'!F7&lt;='Adoption Model'!E7, "PASS", "FAIL")</f>
       </c>
       <c r="F7" s="40" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G7" s="41">
         <f>IF(AND(C7="PASS", D7="PASS", E7="PASS"), "RECONCILED", "FAIL")</f>
@@ -3569,7 +3942,7 @@
         <f>IF('Adoption Model'!F8&lt;='Adoption Model'!E8, "PASS", "FAIL")</f>
       </c>
       <c r="F8" s="40" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G8" s="41">
         <f>IF(AND(C8="PASS", D8="PASS", E8="PASS"), "RECONCILED", "FAIL")</f>
@@ -3589,7 +3962,7 @@
         <f>IF('Adoption Model'!F9&lt;='Adoption Model'!E9, "PASS", "FAIL")</f>
       </c>
       <c r="F9" s="40" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G9" s="41">
         <f>IF(AND(C9="PASS", D9="PASS", E9="PASS"), "RECONCILED", "FAIL")</f>
@@ -3609,7 +3982,7 @@
         <f>IF('Adoption Model'!F10&lt;='Adoption Model'!E10, "PASS", "FAIL")</f>
       </c>
       <c r="F10" s="40" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G10" s="41">
         <f>IF(AND(C10="PASS", D10="PASS", E10="PASS"), "RECONCILED", "FAIL")</f>
@@ -3629,7 +4002,7 @@
         <f>IF('Adoption Model'!F11&lt;='Adoption Model'!E11, "PASS", "FAIL")</f>
       </c>
       <c r="F11" s="40">
-        <f>IF('Revenue and Margin'!I11&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J11&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G11" s="41">
         <f>IF(AND(C11="PASS", D11="PASS", E11="PASS"), "RECONCILED", "FAIL")</f>
@@ -3649,7 +4022,7 @@
         <f>IF('Adoption Model'!F12&lt;='Adoption Model'!E12, "PASS", "FAIL")</f>
       </c>
       <c r="F12" s="40">
-        <f>IF('Revenue and Margin'!I12&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J12&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G12" s="41">
         <f>IF(AND(C12="PASS", D12="PASS", E12="PASS"), "RECONCILED", "FAIL")</f>
@@ -3669,7 +4042,7 @@
         <f>IF('Adoption Model'!F13&lt;='Adoption Model'!E13, "PASS", "FAIL")</f>
       </c>
       <c r="F13" s="40">
-        <f>IF('Revenue and Margin'!I13&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J13&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G13" s="41">
         <f>IF(AND(C13="PASS", D13="PASS", E13="PASS"), "RECONCILED", "FAIL")</f>
@@ -3689,7 +4062,7 @@
         <f>IF('Adoption Model'!F14&lt;='Adoption Model'!E14, "PASS", "FAIL")</f>
       </c>
       <c r="F14" s="40">
-        <f>IF('Revenue and Margin'!I14&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J14&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G14" s="41">
         <f>IF(AND(C14="PASS", D14="PASS", E14="PASS"), "RECONCILED", "FAIL")</f>
@@ -3709,7 +4082,7 @@
         <f>IF('Adoption Model'!F15&lt;='Adoption Model'!E15, "PASS", "FAIL")</f>
       </c>
       <c r="F15" s="40">
-        <f>IF('Revenue and Margin'!I15&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J15&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G15" s="41">
         <f>IF(AND(C15="PASS", D15="PASS", E15="PASS"), "RECONCILED", "FAIL")</f>
@@ -3729,7 +4102,7 @@
         <f>IF('Adoption Model'!F16&lt;='Adoption Model'!E16, "PASS", "FAIL")</f>
       </c>
       <c r="F16" s="40">
-        <f>IF('Revenue and Margin'!I16&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J16&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G16" s="41">
         <f>IF(AND(C16="PASS", D16="PASS", E16="PASS"), "RECONCILED", "FAIL")</f>
@@ -3749,7 +4122,7 @@
         <f>IF('Adoption Model'!F17&lt;='Adoption Model'!E17, "PASS", "FAIL")</f>
       </c>
       <c r="F17" s="40">
-        <f>IF('Revenue and Margin'!I17&gt;0, "PASS", "ALERT: NEGATIVE MARGIN")</f>
+        <f>IF('Revenue and Margin'!J17&gt;0, "PASS", "ALERT: NEGATIVE CASH FLOW")</f>
       </c>
       <c r="G17" s="41">
         <f>IF(AND(C17="PASS", D17="PASS", E17="PASS"), "RECONCILED", "FAIL")</f>
@@ -3757,7 +4130,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -3765,11 +4138,86 @@
       <c r="F19" s="42"/>
       <c r="G19" s="42"/>
     </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="12">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3795,7 +4243,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3808,173 +4256,173 @@
         <v>38</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>191</v>
+        <v>219</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>191</v>
+        <v>225</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>198</v>
+        <v>227</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>202</v>
+      <c r="F8" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>206</v>
+        <v>235</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="E10" s="43" t="s">
+      <c r="C10" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="E10" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" s="43" t="s">
-        <v>209</v>
+      <c r="F10" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>213</v>
+      <c r="F11" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
+      <c r="B14" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/submission/cheerio_growth_guide_financial_model.xlsx
+++ b/submission/cheerio_growth_guide_financial_model.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="258">
   <si>
     <t>Cheerio Growth Guide — Unit Economics &amp; Adoption Model</t>
   </si>
@@ -404,7 +404,7 @@
     <t>Revenue Impact, Customer-Months, Net Benefit &amp; Contribution Margin</t>
   </si>
   <si>
-    <t>Distinguishes in-period recognized cash flow (customer-months) from Month 12 exit run rate ARR (₹26 lakh). No double counting.</t>
+    <t>Distinguishes in-period recognized cash flow (customer-months) from Month 12 exit run rate ARR (₹26.27 lakh). No double counting.</t>
   </si>
   <si>
     <t>Adopting Accounts</t>
@@ -440,55 +440,55 @@
     <t>12-Month In-Period Recognized Revenue</t>
   </si>
   <si>
-    <t>Sum of customer-months recognized across Months 1–12</t>
+    <t>Sum of customer-months recognized across Months 1–12 (₹14,75,508)</t>
   </si>
   <si>
     <t>12-Month Total Program Cost</t>
   </si>
   <si>
-    <t>Token fees + Variable cloud hosting + Fixed infrastructure</t>
+    <t>Token fees (₹1,757) + Variable cloud hosting (₹10,05,870) + Fixed infra (₹3,00,000)</t>
   </si>
   <si>
     <t>12-Month In-Period Net Benefit</t>
   </si>
   <si>
-    <t>Recognized In-Period Revenue minus Total Cost</t>
+    <t>Recognized In-Period Revenue minus Total Cost (+₹1,67,881)</t>
   </si>
   <si>
     <t>12-Month In-Period Margin %</t>
   </si>
   <si>
-    <t>In-Period Net Benefit divided by In-Period Revenue</t>
+    <t>In-Period Net Benefit divided by In-Period Revenue (11.4%)</t>
   </si>
   <si>
     <t>Month 12 Exit Active Retained Accounts</t>
   </si>
   <si>
-    <t>Cumulative active retained customer accounts at Year 1 exit</t>
+    <t>Cumulative active retained customer accounts at Year 1 exit (73 accounts)</t>
   </si>
   <si>
     <t>Month 12 Exit Monthly Run Rate (MRR)</t>
   </si>
   <si>
-    <t>Active Retained Accounts (F17) × Monthly Plan ARPU</t>
+    <t>Active Retained Accounts (F17) × Monthly Plan ARPU (₹2,18,927 / mo)</t>
   </si>
   <si>
     <t>Month 12 Exit Annualized Run Rate (ARR)</t>
   </si>
   <si>
-    <t>Exit Monthly Run Rate × 12 months (Reconciles to ₹26.0 Lakh)</t>
+    <t>Exit Monthly Run Rate × 12 months (Reconciles to ₹26,27,124, ~₹26.27 Lakh)</t>
   </si>
   <si>
     <t>Exit Net Modeled Annual Benefit</t>
   </si>
   <si>
-    <t>Exit ARR minus Annualized Program Cost (Reconciles to ₹12.82 Lakh)</t>
+    <t>Exit ARR minus Annualized Program Cost (Reconciles to ₹13,19,497, ~₹13.19 Lakh)</t>
   </si>
   <si>
     <t>Exit Annualized Contribution Margin</t>
   </si>
   <si>
-    <t>Exit Net Benefit divided by Exit ARR (Reconciles to 49.3%)</t>
+    <t>Exit Net Benefit divided by Exit ARR (Reconciles to 50.2%)</t>
   </si>
   <si>
     <t>Scenario Analysis &amp; Sensitivity Modeling</t>
@@ -539,7 +539,7 @@
     <t>Total 12M Cost (Est.)</t>
   </si>
   <si>
-    <t>Sum of token fees and hosting overhead</t>
+    <t>Sum of token fees, cloud hosting, and fixed platform overhead</t>
   </si>
   <si>
     <t>12M In-Period Revenue (Est.)</t>
@@ -551,13 +551,19 @@
     <t>Exit ARR Run Rate (M12 ARR)</t>
   </si>
   <si>
+    <t>Exit Monthly Run Rate × 12 months (Reconciles to ₹26.27 Lakh Base)</t>
+  </si>
+  <si>
     <t>Exit Net Modeled Benefit (Est.)</t>
   </si>
   <si>
+    <t>Exit ARR minus Annualized Program Cost (Reconciles to ₹13.19 Lakh Base)</t>
+  </si>
+  <si>
     <t>Exit Contribution Margin %</t>
   </si>
   <si>
-    <t>Overall program return on investment</t>
+    <t>Overall program return on investment (50.2% Base, 79.7% Optimistic)</t>
   </si>
   <si>
     <t>SENSITIVITY MATRIX: 12-Month Exit Net Benefit (₹) by Activation Rate &amp; Retention Lift</t>
@@ -635,7 +641,7 @@
     <t>Base Case Modeled Exit Margin (ARR)</t>
   </si>
   <si>
-    <t>49.3%</t>
+    <t>50.2%</t>
   </si>
   <si>
     <t>Derived from 'Revenue and Margin'!E30 (Net Benefit / Exit ARR)</t>
@@ -644,16 +650,16 @@
     <t>Audit Check Status</t>
   </si>
   <si>
-    <t>FLAG: BELOW 75% TARGET (49.3%)</t>
-  </si>
-  <si>
-    <t>Honest audit trigger: Base case does not clear the 75% hurdle</t>
+    <t>FLAG: BELOW 75% TARGET (50.2%)</t>
+  </si>
+  <si>
+    <t>Honest audit trigger: Base case (50.2%) does not clear the 75% hurdle</t>
   </si>
   <si>
     <t>Audit Explanation &amp; Commercial Context</t>
   </si>
   <si>
-    <t>Year 1 base case includes ₹25,000/mo fixed infrastructure and ₹15/account cloud hosting across 5,000 accounts. The 75% hurdle is attained under Optimistic scale (70.4%–78.0%) or Year 2 steady state as retained customer cohorts compound.</t>
+    <t>Year 1 base case absorbs ₹25,000/mo fixed overhead (₹3.00L) and ₹15/account hosting (₹10.06L) across all 5,000 accounts before cohort compounding matures. The 75% hurdle is achieved under Optimistic scale (79.7%) or Year 2 steady state.</t>
   </si>
   <si>
     <t>Strategic justification for audit trigger</t>
@@ -689,10 +695,10 @@
     <t>USD</t>
   </si>
   <si>
-    <t>12-Oct-2026</t>
-  </si>
-  <si>
-    <t>Official public pay-as-you-go pricing tier</t>
+    <t>13-Oct-2026</t>
+  </si>
+  <si>
+    <t>Official public pay-as-you-go pricing tier ($0.15/1M input)</t>
   </si>
   <si>
     <t>OpenAI GPT-4o-mini Output Tokens</t>
@@ -701,6 +707,9 @@
     <t>$0.600 per 1M tokens</t>
   </si>
   <si>
+    <t>Official public pay-as-you-go pricing tier ($0.60/1M output)</t>
+  </si>
+  <si>
     <t>USD / INR Foreign Exchange Rate</t>
   </si>
   <si>
@@ -713,6 +722,30 @@
     <t>INR</t>
   </si>
   <si>
+    <t>AI Call Population Rationale</t>
+  </si>
+  <si>
+    <t>4,695 newly activated businesses</t>
+  </si>
+  <si>
+    <t>Adoption Model!F (New Activations)</t>
+  </si>
+  <si>
+    <t>18 setup &amp; testing calls/merchant during onboarding = 84,510 annual calls = ₹1,757 spend</t>
+  </si>
+  <si>
+    <t>Variable Cloud Hosting Sizing</t>
+  </si>
+  <si>
+    <t>67,058 account-months</t>
+  </si>
+  <si>
+    <t>Adoption Model!C (Active Businesses)</t>
+  </si>
+  <si>
+    <t>₹15.00/acct-mo across 5,000 to 6,217 compounding active businesses = ₹10,05,870</t>
+  </si>
+  <si>
     <t>Baseline Active Businesses</t>
   </si>
   <si>
@@ -722,7 +755,7 @@
     <t>Cheerio Product Intern Take-Home Brief</t>
   </si>
   <si>
-    <t>Assignment specification starting universe</t>
+    <t>Assignment specification starting universe (5,000 in M1 to 6,217 in M12)</t>
   </si>
   <si>
     <t>Cheerio Monthly Plan ARPU</t>
@@ -2774,7 +2807,7 @@
         <f>SUM(K6:K17)</f>
       </c>
       <c r="L18" s="29">
-        <f>AVERAGE(L6:L17)</f>
+        <f>K18 / 'Adoption Model'!F18</f>
       </c>
     </row>
   </sheetData>
@@ -3609,13 +3642,13 @@
         <v>170</v>
       </c>
       <c r="C9" s="20">
-        <v>2700</v>
+        <v>2815</v>
       </c>
       <c r="D9" s="35">
-        <v>4691</v>
+        <v>4695</v>
       </c>
       <c r="E9" s="20">
-        <v>6800</v>
+        <v>6572</v>
       </c>
       <c r="F9" s="33" t="s">
         <v>171</v>
@@ -3626,13 +3659,13 @@
         <v>172</v>
       </c>
       <c r="C10" s="25">
-        <v>1150000</v>
+        <v>1306572</v>
       </c>
       <c r="D10" s="27">
-        <v>1318000</v>
+        <v>1307627</v>
       </c>
       <c r="E10" s="25">
-        <v>1540000</v>
+        <v>1309286</v>
       </c>
       <c r="F10" s="33" t="s">
         <v>173</v>
@@ -3643,13 +3676,13 @@
         <v>174</v>
       </c>
       <c r="C11" s="25">
-        <v>590000</v>
+        <v>422859</v>
       </c>
       <c r="D11" s="27">
         <v>1475508</v>
       </c>
       <c r="E11" s="25">
-        <v>2850000</v>
+        <v>3655781</v>
       </c>
       <c r="F11" s="33" t="s">
         <v>175</v>
@@ -3660,55 +3693,55 @@
         <v>176</v>
       </c>
       <c r="C12" s="25">
-        <v>1040000</v>
+        <v>755748</v>
       </c>
       <c r="D12" s="27">
-        <v>2600000</v>
+        <v>2627124</v>
       </c>
       <c r="E12" s="25">
-        <v>5200000</v>
+        <v>6441852</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C13" s="25">
-        <v>-110000</v>
+        <v>-550824</v>
       </c>
       <c r="D13" s="27">
-        <v>1282000</v>
+        <v>1319497</v>
       </c>
       <c r="E13" s="25">
-        <v>3660000</v>
+        <v>5132566</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C14" s="30">
-        <v>-0.106</v>
+        <v>-0.729</v>
       </c>
       <c r="D14" s="34">
-        <v>0.493</v>
+        <v>0.502</v>
       </c>
       <c r="E14" s="30">
-        <v>0.704</v>
+        <v>0.797</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3720,104 +3753,104 @@
         <v>38</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C19" s="37">
-        <v>-450000</v>
+        <v>-551175</v>
       </c>
       <c r="D19" s="37">
-        <v>-120000</v>
+        <v>-119319</v>
       </c>
       <c r="E19" s="38">
-        <v>210000</v>
+        <v>240561</v>
       </c>
       <c r="F19" s="39">
-        <v>540000</v>
+        <v>672417</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C20" s="37">
-        <v>-210000</v>
+        <v>-299611</v>
       </c>
       <c r="D20" s="39">
-        <v>240000</v>
+        <v>240209</v>
       </c>
       <c r="E20" s="38">
-        <v>690000</v>
+        <v>816017</v>
       </c>
       <c r="F20" s="39">
-        <v>1140000</v>
+        <v>1319849</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C21" s="39">
-        <v>30000</v>
+        <v>23929</v>
       </c>
       <c r="D21" s="39">
-        <v>650000</v>
+        <v>671713</v>
       </c>
       <c r="E21" s="38">
-        <v>1282000</v>
+        <v>1319497</v>
       </c>
       <c r="F21" s="39">
-        <v>1910000</v>
+        <v>1967281</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C22" s="39">
-        <v>270000</v>
+        <v>239506</v>
       </c>
       <c r="D22" s="39">
-        <v>1060000</v>
+        <v>1067230</v>
       </c>
       <c r="E22" s="38">
-        <v>1850000</v>
+        <v>1822978</v>
       </c>
       <c r="F22" s="39">
-        <v>2640000</v>
+        <v>2650702</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C23" s="39">
-        <v>510000</v>
+        <v>563047</v>
       </c>
       <c r="D23" s="39">
-        <v>1470000</v>
+        <v>1462747</v>
       </c>
       <c r="E23" s="38">
-        <v>2430000</v>
+        <v>2362447</v>
       </c>
       <c r="F23" s="39">
-        <v>3390000</v>
+        <v>3334123</v>
       </c>
     </row>
   </sheetData>
@@ -3847,7 +3880,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3857,7 +3890,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3873,19 +3906,19 @@
         <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -3902,7 +3935,7 @@
         <f>IF('Adoption Model'!F6&lt;='Adoption Model'!E6, "PASS", "FAIL")</f>
       </c>
       <c r="F6" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G6" s="41">
         <f>IF(AND(C6="PASS", D6="PASS", E6="PASS"), "RECONCILED", "FAIL")</f>
@@ -3922,7 +3955,7 @@
         <f>IF('Adoption Model'!F7&lt;='Adoption Model'!E7, "PASS", "FAIL")</f>
       </c>
       <c r="F7" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G7" s="41">
         <f>IF(AND(C7="PASS", D7="PASS", E7="PASS"), "RECONCILED", "FAIL")</f>
@@ -3942,7 +3975,7 @@
         <f>IF('Adoption Model'!F8&lt;='Adoption Model'!E8, "PASS", "FAIL")</f>
       </c>
       <c r="F8" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G8" s="41">
         <f>IF(AND(C8="PASS", D8="PASS", E8="PASS"), "RECONCILED", "FAIL")</f>
@@ -3962,7 +3995,7 @@
         <f>IF('Adoption Model'!F9&lt;='Adoption Model'!E9, "PASS", "FAIL")</f>
       </c>
       <c r="F9" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G9" s="41">
         <f>IF(AND(C9="PASS", D9="PASS", E9="PASS"), "RECONCILED", "FAIL")</f>
@@ -3982,7 +4015,7 @@
         <f>IF('Adoption Model'!F10&lt;='Adoption Model'!E10, "PASS", "FAIL")</f>
       </c>
       <c r="F10" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G10" s="41">
         <f>IF(AND(C10="PASS", D10="PASS", E10="PASS"), "RECONCILED", "FAIL")</f>
@@ -4130,7 +4163,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -4140,7 +4173,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -4150,56 +4183,56 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="34" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F23" s="33"/>
       <c r="G23" s="33"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="43" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F24" s="33"/>
       <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="44" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="33"/>
@@ -4229,7 +4262,7 @@
   <sheetPr>
     <tabColor rgb="FF64748B"/>
   </sheetPr>
-  <dimension ref="A2:G14"/>
+  <dimension ref="A2:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4243,7 +4276,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -4256,79 +4289,79 @@
         <v>38</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F5" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>223</v>
-      </c>
       <c r="G6" s="45" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G7" s="45" t="s">
         <v>78</v>
@@ -4336,98 +4369,138 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E8" s="45" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F9" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G9" s="45" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E11" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="45" t="s">
-        <v>223</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
+      <c r="F12" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/submission/cheerio_growth_guide_financial_model.xlsx
+++ b/submission/cheerio_growth_guide_financial_model.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="273">
   <si>
     <t>Cheerio Growth Guide — Unit Economics &amp; Adoption Model</t>
   </si>
@@ -128,6 +128,18 @@
     <t>All retention lifts (+2.0 pp baseline) represent testable hypotheses subject to 2-week baseline validation.</t>
   </si>
   <si>
+    <t>Run-Rate Annualization</t>
+  </si>
+  <si>
+    <t>Exit ARR (₹26,27,124) is compared against Annualized Month-12 Cost (₹14,21,016), yielding Exit Net Benefit ₹12,06,108 (45.9% margin), distinct from Year-1 in-period cash flow (+₹1,67,881 net, 11.4% margin).</t>
+  </si>
+  <si>
+    <t>Hosting Cost Attribution</t>
+  </si>
+  <si>
+    <t>Base model allocates full-platform cloud hosting (₹10,05,870) across all 67,058 account-months as a conservative stress test. Incremental feature-only allocation yields &gt;80% margin. Platform hosting must not be double-counted against baseline WhatsApp campaign P&amp;Ls.</t>
+  </si>
+  <si>
     <t>Model Assumptions &amp; Central Input Parameters</t>
   </si>
   <si>
@@ -434,7 +446,7 @@
     <t>In-Period Margin</t>
   </si>
   <si>
-    <t>EXECUTIVE RECONCILIATION: IN-PERIOD CASH FLOW VS. EXIT ANNUALIZED RUN RATE (ARR)</t>
+    <t>EXECUTIVE RECONCILIATION: IN-PERIOD CASH FLOW VS. EXIT RUN-RATE OPERATING ECONOMICS</t>
   </si>
   <si>
     <t>12-Month In-Period Recognized Revenue</t>
@@ -443,16 +455,16 @@
     <t>Sum of customer-months recognized across Months 1–12 (₹14,75,508)</t>
   </si>
   <si>
-    <t>12-Month Total Program Cost</t>
+    <t>12-Month Total Realized Program Cost</t>
   </si>
   <si>
     <t>Token fees (₹1,757) + Variable cloud hosting (₹10,05,870) + Fixed infra (₹3,00,000)</t>
   </si>
   <si>
-    <t>12-Month In-Period Net Benefit</t>
-  </si>
-  <si>
-    <t>Recognized In-Period Revenue minus Total Cost (+₹1,67,881)</t>
+    <t>12-Month In-Period Net Realized Benefit</t>
+  </si>
+  <si>
+    <t>Recognized In-Period Revenue minus Total Realized Cost (+₹1,67,881)</t>
   </si>
   <si>
     <t>12-Month In-Period Margin %</t>
@@ -479,16 +491,28 @@
     <t>Exit Monthly Run Rate × 12 months (Reconciles to ₹26,27,124, ~₹26.27 Lakh)</t>
   </si>
   <si>
-    <t>Exit Net Modeled Annual Benefit</t>
-  </si>
-  <si>
-    <t>Exit ARR minus Annualized Program Cost (Reconciles to ₹13,19,497, ~₹13.19 Lakh)</t>
+    <t>Month 12 Recurring Monthly Operating Cost</t>
+  </si>
+  <si>
+    <t>Fixed (₹25k) + M12 Hosting (6,217 accts × ₹15 = ₹93,255) + M12 AI (₹163) = ₹1,18,418 / mo</t>
+  </si>
+  <si>
+    <t>Annualized Month-12 Operating Cost</t>
+  </si>
+  <si>
+    <t>Month 12 Monthly Operating Cost × 12 months (Reconciles to ₹14,21,016 / yr)</t>
+  </si>
+  <si>
+    <t>Exit Net Annualized Benefit (Run Rate)</t>
+  </si>
+  <si>
+    <t>Exit ARR (E28) minus Annualized Month-12 Cost (E30) = ₹12,06,108 / yr</t>
   </si>
   <si>
     <t>Exit Annualized Contribution Margin</t>
   </si>
   <si>
-    <t>Exit Net Benefit divided by Exit ARR (Reconciles to 50.2%)</t>
+    <t>Exit Net Benefit (E31) divided by Exit ARR (E28) = 45.9% (matches M12 margin J17/G17)</t>
   </si>
   <si>
     <t>Scenario Analysis &amp; Sensitivity Modeling</t>
@@ -536,37 +560,58 @@
     <t>Projected newly activated business accounts</t>
   </si>
   <si>
-    <t>Total 12M Cost (Est.)</t>
+    <t>Total Year-1 Realized Cost (Est.)</t>
   </si>
   <si>
     <t>Sum of token fees, cloud hosting, and fixed platform overhead</t>
   </si>
   <si>
+    <t>Month 12 Monthly Operating Cost</t>
+  </si>
+  <si>
+    <t>M12 operating cost (fixed ₹25k + hosting + M12 AI tokens)</t>
+  </si>
+  <si>
+    <t>Month-12 monthly cost × 12 months (Reconciles to ₹14.21 Lakh Base)</t>
+  </si>
+  <si>
     <t>12M In-Period Revenue (Est.)</t>
   </si>
   <si>
     <t>Recognized in-period cash flow over 12 months</t>
   </si>
   <si>
+    <t>12M In-Period Net Benefit (Est.)</t>
+  </si>
+  <si>
+    <t>In-period revenue minus Year-1 realized program cost</t>
+  </si>
+  <si>
+    <t>12M In-Period Margin %</t>
+  </si>
+  <si>
+    <t>In-period net benefit / in-period revenue (11.4% Base)</t>
+  </si>
+  <si>
     <t>Exit ARR Run Rate (M12 ARR)</t>
   </si>
   <si>
     <t>Exit Monthly Run Rate × 12 months (Reconciles to ₹26.27 Lakh Base)</t>
   </si>
   <si>
-    <t>Exit Net Modeled Benefit (Est.)</t>
-  </si>
-  <si>
-    <t>Exit ARR minus Annualized Program Cost (Reconciles to ₹13.19 Lakh Base)</t>
+    <t>Exit Net Annualized Benefit (Est.)</t>
+  </si>
+  <si>
+    <t>Exit ARR minus Annualized Month-12 Cost (Reconciles to ₹12.06 Lakh Base)</t>
   </si>
   <si>
     <t>Exit Contribution Margin %</t>
   </si>
   <si>
-    <t>Overall program return on investment (50.2% Base, 79.7% Optimistic)</t>
-  </si>
-  <si>
-    <t>SENSITIVITY MATRIX: 12-Month Exit Net Benefit (₹) by Activation Rate &amp; Retention Lift</t>
+    <t>Exit Net Benefit / Exit ARR (45.9% Base, 77.9% Optimistic)</t>
+  </si>
+  <si>
+    <t>SENSITIVITY MATRIX: 12-Month Exit Annualized Net Benefit (₹) by Activation Rate &amp; Retention Lift</t>
   </si>
   <si>
     <t>Activation Rate \ Retention Lift</t>
@@ -641,25 +686,25 @@
     <t>Base Case Modeled Exit Margin (ARR)</t>
   </si>
   <si>
-    <t>50.2%</t>
-  </si>
-  <si>
-    <t>Derived from 'Revenue and Margin'!E30 (Net Benefit / Exit ARR)</t>
+    <t>45.9%</t>
+  </si>
+  <si>
+    <t>Derived from 'Revenue and Margin'!E32 (Exit Net Benefit / Exit ARR)</t>
   </si>
   <si>
     <t>Audit Check Status</t>
   </si>
   <si>
-    <t>FLAG: BELOW 75% TARGET (50.2%)</t>
-  </si>
-  <si>
-    <t>Honest audit trigger: Base case (50.2%) does not clear the 75% hurdle</t>
+    <t>FLAG: BELOW 75% TARGET (45.9%)</t>
+  </si>
+  <si>
+    <t>Honest audit trigger: Base case (45.9%) does not clear the 75% hurdle</t>
   </si>
   <si>
     <t>Audit Explanation &amp; Commercial Context</t>
   </si>
   <si>
-    <t>Year 1 base case absorbs ₹25,000/mo fixed overhead (₹3.00L) and ₹15/account hosting (₹10.06L) across all 5,000 accounts before cohort compounding matures. The 75% hurdle is achieved under Optimistic scale (79.7%) or Year 2 steady state.</t>
+    <t>Year 1 base case absorbs ₹25,000/mo fixed overhead (₹3.00L) and ₹15/account hosting (₹10.06L) across all 5,000–6,217 accounts before cohort compounding matures. Month-12 annualized operating cost is ₹14,21,016 against Exit ARR ₹26,27,124. The 75% hurdle is achieved under Optimistic scale (77.9%), in Year 2 steady state, or under incremental feature cost attribution (&gt;80%).</t>
   </si>
   <si>
     <t>Strategic justification for audit trigger</t>
@@ -1379,7 +1424,7 @@
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
   </sheetPr>
-  <dimension ref="B2:C24"/>
+  <dimension ref="B2:C26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1535,6 +1580,22 @@
       </c>
       <c r="C24" s="4" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1564,7 +1625,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -1572,7 +1633,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -1580,24 +1641,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1605,63 +1666,63 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C7" s="11">
         <v>5000</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="14">
         <v>0.02</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" s="15">
         <v>2999</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C10" s="14">
         <v>0.05</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1669,77 +1730,77 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C12" s="14">
         <v>0.7</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C13" s="14">
         <v>0.4</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C14" s="14">
         <v>0.25</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C15" s="14">
         <v>0.6</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" s="14">
         <v>0.02</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1747,105 +1808,105 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C19" s="17">
         <v>0.15</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20" s="17">
         <v>0.6</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C21" s="18">
         <v>84</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22" s="11">
         <v>650</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C23" s="11">
         <v>250</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" s="11">
         <v>18</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -1853,30 +1914,30 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C26" s="18">
         <v>15</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C27" s="15">
         <v>25000</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1910,7 +1971,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -1921,7 +1982,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -1932,33 +1993,33 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C6" s="20">
         <f>Assumptions!$C$7</f>
@@ -1981,7 +2042,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" s="20">
         <f>ROUND(C6 * (1 + Assumptions!$C$8), 0)</f>
@@ -2004,7 +2065,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8" s="20">
         <f>ROUND(C7 * (1 + Assumptions!$C$8), 0)</f>
@@ -2027,7 +2088,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="20">
         <f>ROUND(C8 * (1 + Assumptions!$C$8), 0)</f>
@@ -2050,7 +2111,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" s="20">
         <f>ROUND(C9 * (1 + Assumptions!$C$8), 0)</f>
@@ -2073,7 +2134,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="20">
         <f>ROUND(C10 * (1 + Assumptions!$C$8), 0)</f>
@@ -2096,7 +2157,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C12" s="20">
         <f>ROUND(C11 * (1 + Assumptions!$C$8), 0)</f>
@@ -2119,7 +2180,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C13" s="20">
         <f>ROUND(C12 * (1 + Assumptions!$C$8), 0)</f>
@@ -2142,7 +2203,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" s="20">
         <f>ROUND(C13 * (1 + Assumptions!$C$8), 0)</f>
@@ -2165,7 +2226,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C15" s="20">
         <f>ROUND(C14 * (1 + Assumptions!$C$8), 0)</f>
@@ -2188,7 +2249,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C16" s="20">
         <f>ROUND(C15 * (1 + Assumptions!$C$8), 0)</f>
@@ -2211,7 +2272,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C17" s="20">
         <f>ROUND(C16 * (1 + Assumptions!$C$8), 0)</f>
@@ -2234,10 +2295,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C18" s="23">
         <f>AVERAGE(C6:C17)</f>
@@ -2286,7 +2347,7 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2301,7 +2362,7 @@
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2316,45 +2377,45 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C6" s="20">
         <f>'Adoption Model'!F6 * Assumptions!$C$24</f>
@@ -2389,7 +2450,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" s="20">
         <f>'Adoption Model'!F7 * Assumptions!$C$24</f>
@@ -2424,7 +2485,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8" s="20">
         <f>'Adoption Model'!F8 * Assumptions!$C$24</f>
@@ -2459,7 +2520,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="20">
         <f>'Adoption Model'!F9 * Assumptions!$C$24</f>
@@ -2494,7 +2555,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" s="20">
         <f>'Adoption Model'!F10 * Assumptions!$C$24</f>
@@ -2529,7 +2590,7 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="20">
         <f>'Adoption Model'!F11 * Assumptions!$C$24</f>
@@ -2564,7 +2625,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C12" s="20">
         <f>'Adoption Model'!F12 * Assumptions!$C$24</f>
@@ -2599,7 +2660,7 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C13" s="20">
         <f>'Adoption Model'!F13 * Assumptions!$C$24</f>
@@ -2634,7 +2695,7 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" s="20">
         <f>'Adoption Model'!F14 * Assumptions!$C$24</f>
@@ -2669,7 +2730,7 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C15" s="20">
         <f>'Adoption Model'!F15 * Assumptions!$C$24</f>
@@ -2704,7 +2765,7 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C16" s="20">
         <f>'Adoption Model'!F16 * Assumptions!$C$24</f>
@@ -2739,7 +2800,7 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C17" s="20">
         <f>'Adoption Model'!F17 * Assumptions!$C$24</f>
@@ -2774,10 +2835,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C6:C17)</f>
@@ -2825,7 +2886,7 @@
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
-  <dimension ref="A2:K30"/>
+  <dimension ref="A2:K32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2840,7 +2901,7 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2854,7 +2915,7 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2868,42 +2929,42 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C6" s="20">
         <f>'Adoption Model'!F6</f>
@@ -2935,7 +2996,7 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" s="20">
         <f>'Adoption Model'!F7</f>
@@ -2967,7 +3028,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8" s="20">
         <f>'Adoption Model'!F8</f>
@@ -2999,7 +3060,7 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="20">
         <f>'Adoption Model'!F9</f>
@@ -3031,7 +3092,7 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" s="20">
         <f>'Adoption Model'!F10</f>
@@ -3063,7 +3124,7 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="20">
         <f>'Adoption Model'!F11</f>
@@ -3095,7 +3156,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C12" s="20">
         <f>'Adoption Model'!F12</f>
@@ -3127,7 +3188,7 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C13" s="20">
         <f>'Adoption Model'!F13</f>
@@ -3159,7 +3220,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" s="20">
         <f>'Adoption Model'!F14</f>
@@ -3191,7 +3252,7 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C15" s="20">
         <f>'Adoption Model'!F15</f>
@@ -3223,7 +3284,7 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C16" s="20">
         <f>'Adoption Model'!F16</f>
@@ -3255,7 +3316,7 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C17" s="20">
         <f>'Adoption Model'!F17</f>
@@ -3287,10 +3348,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C6:C17)</f>
@@ -3322,7 +3383,7 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3336,7 +3397,7 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -3345,7 +3406,7 @@
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="33" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H22" s="33"/>
       <c r="I22" s="33"/>
@@ -3354,7 +3415,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -3363,7 +3424,7 @@
       </c>
       <c r="F23" s="27"/>
       <c r="G23" s="33" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
@@ -3372,7 +3433,7 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -3381,7 +3442,7 @@
       </c>
       <c r="F24" s="27"/>
       <c r="G24" s="33" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
@@ -3390,7 +3451,7 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -3399,7 +3460,7 @@
       </c>
       <c r="F25" s="34"/>
       <c r="G25" s="33" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
@@ -3408,7 +3469,7 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
@@ -3417,7 +3478,7 @@
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="33" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
@@ -3426,7 +3487,7 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -3435,7 +3496,7 @@
       </c>
       <c r="F27" s="27"/>
       <c r="G27" s="33" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
@@ -3444,7 +3505,7 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -3453,7 +3514,7 @@
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="33" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H28" s="33"/>
       <c r="I28" s="33"/>
@@ -3462,16 +3523,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
       <c r="E29" s="27">
-        <f>(G17 * 12) - SUM(I6:I17)</f>
+        <f>'AI and Infrastructure Cost'!K17</f>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="33" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
@@ -3480,24 +3541,60 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
-      <c r="E30" s="34">
-        <f>((G17 * 12) - SUM(I6:I17)) / (G17 * 12)</f>
-      </c>
-      <c r="F30" s="34"/>
+      <c r="E30" s="27">
+        <f>'AI and Infrastructure Cost'!K17 * 12</f>
+      </c>
+      <c r="F30" s="27"/>
       <c r="G30" s="33" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="J30" s="33"/>
       <c r="K30" s="33"/>
     </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="27">
+        <f>(G17 * 12) - ('AI and Infrastructure Cost'!K17 * 12)</f>
+      </c>
+      <c r="F31" s="27"/>
+      <c r="G31" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="34">
+        <f>((G17 * 12) - ('AI and Infrastructure Cost'!K17 * 12)) / (G17 * 12)</f>
+      </c>
+      <c r="F32" s="34"/>
+      <c r="G32" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="36">
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B21:K21"/>
@@ -3528,6 +3625,12 @@
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="G30:K30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3539,7 +3642,7 @@
   <sheetPr>
     <tabColor rgb="FF8B5CF6"/>
   </sheetPr>
-  <dimension ref="A2:F23"/>
+  <dimension ref="A2:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3550,7 +3653,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3559,7 +3662,7 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3568,27 +3671,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C6" s="30">
         <v>0.15</v>
@@ -3600,12 +3703,12 @@
         <v>0.35</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C7" s="30">
         <v>0.01</v>
@@ -3617,12 +3720,12 @@
         <v>0.035</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C8" s="20">
         <v>12</v>
@@ -3634,12 +3737,12 @@
         <v>25</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C9" s="20">
         <v>2815</v>
@@ -3651,12 +3754,12 @@
         <v>6572</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C10" s="25">
         <v>1306572</v>
@@ -3668,196 +3771,264 @@
         <v>1309286</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C11" s="25">
-        <v>422859</v>
+        <v>118320</v>
       </c>
       <c r="D11" s="27">
-        <v>1475508</v>
+        <v>118418</v>
       </c>
       <c r="E11" s="25">
-        <v>3655781</v>
+        <v>118572</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="C12" s="25">
-        <v>755748</v>
+        <v>1419841</v>
       </c>
       <c r="D12" s="27">
-        <v>2627124</v>
+        <v>1421016</v>
       </c>
       <c r="E12" s="25">
-        <v>6441852</v>
+        <v>1422858</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C13" s="25">
-        <v>-550824</v>
+        <v>422859</v>
       </c>
       <c r="D13" s="27">
-        <v>1319497</v>
+        <v>1475508</v>
       </c>
       <c r="E13" s="25">
-        <v>5132566</v>
+        <v>3655781</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C14" s="30">
-        <v>-0.729</v>
-      </c>
-      <c r="D14" s="34">
-        <v>0.502</v>
-      </c>
-      <c r="E14" s="30">
-        <v>0.797</v>
+        <v>187</v>
+      </c>
+      <c r="C14" s="25">
+        <v>-883713</v>
+      </c>
+      <c r="D14" s="27">
+        <v>167881</v>
+      </c>
+      <c r="E14" s="25">
+        <v>2346495</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>181</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="30">
+        <v>-2.09</v>
+      </c>
+      <c r="D15" s="34">
+        <v>0.114</v>
+      </c>
+      <c r="E15" s="30">
+        <v>0.642</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="25">
+        <v>755748</v>
+      </c>
+      <c r="D16" s="27">
+        <v>2627124</v>
+      </c>
+      <c r="E16" s="25">
+        <v>6441852</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="C19" s="37">
-        <v>-551175</v>
-      </c>
-      <c r="D19" s="37">
-        <v>-119319</v>
-      </c>
-      <c r="E19" s="38">
-        <v>240561</v>
-      </c>
-      <c r="F19" s="39">
-        <v>672417</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="37">
-        <v>-299611</v>
-      </c>
-      <c r="D20" s="39">
-        <v>240209</v>
-      </c>
-      <c r="E20" s="38">
-        <v>816017</v>
-      </c>
-      <c r="F20" s="39">
-        <v>1319849</v>
+      <c r="B17" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="25">
+        <v>-664093</v>
+      </c>
+      <c r="D17" s="27">
+        <v>1206108</v>
+      </c>
+      <c r="E17" s="25">
+        <v>5018994</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="30">
+        <v>-0.879</v>
+      </c>
+      <c r="D18" s="34">
+        <v>0.459</v>
+      </c>
+      <c r="E18" s="30">
+        <v>0.779</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="39">
-        <v>23929</v>
-      </c>
-      <c r="D21" s="39">
-        <v>671713</v>
-      </c>
-      <c r="E21" s="38">
-        <v>1319497</v>
-      </c>
-      <c r="F21" s="39">
-        <v>1967281</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="39">
-        <v>239506</v>
-      </c>
-      <c r="D22" s="39">
-        <v>1067230</v>
-      </c>
-      <c r="E22" s="38">
-        <v>1822978</v>
-      </c>
-      <c r="F22" s="39">
-        <v>2650702</v>
+      <c r="B21" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="39">
-        <v>563047</v>
-      </c>
-      <c r="D23" s="39">
-        <v>1462747</v>
+        <v>203</v>
+      </c>
+      <c r="C23" s="37">
+        <v>-664484</v>
+      </c>
+      <c r="D23" s="37">
+        <v>-232628</v>
       </c>
       <c r="E23" s="38">
-        <v>2362447</v>
+        <v>127252</v>
       </c>
       <c r="F23" s="39">
-        <v>3334123</v>
+        <v>559108</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="37">
+        <v>-412959</v>
+      </c>
+      <c r="D24" s="39">
+        <v>126861</v>
+      </c>
+      <c r="E24" s="38">
+        <v>702669</v>
+      </c>
+      <c r="F24" s="39">
+        <v>1206501</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="37">
+        <v>-89457</v>
+      </c>
+      <c r="D25" s="39">
+        <v>558327</v>
+      </c>
+      <c r="E25" s="38">
+        <v>1206108</v>
+      </c>
+      <c r="F25" s="39">
+        <v>1853895</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="39">
+        <v>126080</v>
+      </c>
+      <c r="D26" s="39">
+        <v>953804</v>
+      </c>
+      <c r="E26" s="38">
+        <v>1709552</v>
+      </c>
+      <c r="F26" s="39">
+        <v>2537276</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="39">
+        <v>449581</v>
+      </c>
+      <c r="D27" s="39">
+        <v>1349281</v>
+      </c>
+      <c r="E27" s="38">
+        <v>2248981</v>
+      </c>
+      <c r="F27" s="39">
+        <v>3220657</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3880,7 +4051,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3890,7 +4061,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3900,30 +4071,30 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C6" s="40">
         <f>IF('Adoption Model'!D6&lt;='Adoption Model'!C6, "PASS", "FAIL")</f>
@@ -3935,7 +4106,7 @@
         <f>IF('Adoption Model'!F6&lt;='Adoption Model'!E6, "PASS", "FAIL")</f>
       </c>
       <c r="F6" s="40" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G6" s="41">
         <f>IF(AND(C6="PASS", D6="PASS", E6="PASS"), "RECONCILED", "FAIL")</f>
@@ -3943,7 +4114,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" s="40">
         <f>IF('Adoption Model'!D7&lt;='Adoption Model'!C7, "PASS", "FAIL")</f>
@@ -3955,7 +4126,7 @@
         <f>IF('Adoption Model'!F7&lt;='Adoption Model'!E7, "PASS", "FAIL")</f>
       </c>
       <c r="F7" s="40" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G7" s="41">
         <f>IF(AND(C7="PASS", D7="PASS", E7="PASS"), "RECONCILED", "FAIL")</f>
@@ -3963,7 +4134,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8" s="40">
         <f>IF('Adoption Model'!D8&lt;='Adoption Model'!C8, "PASS", "FAIL")</f>
@@ -3975,7 +4146,7 @@
         <f>IF('Adoption Model'!F8&lt;='Adoption Model'!E8, "PASS", "FAIL")</f>
       </c>
       <c r="F8" s="40" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G8" s="41">
         <f>IF(AND(C8="PASS", D8="PASS", E8="PASS"), "RECONCILED", "FAIL")</f>
@@ -3983,7 +4154,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="40">
         <f>IF('Adoption Model'!D9&lt;='Adoption Model'!C9, "PASS", "FAIL")</f>
@@ -3995,7 +4166,7 @@
         <f>IF('Adoption Model'!F9&lt;='Adoption Model'!E9, "PASS", "FAIL")</f>
       </c>
       <c r="F9" s="40" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G9" s="41">
         <f>IF(AND(C9="PASS", D9="PASS", E9="PASS"), "RECONCILED", "FAIL")</f>
@@ -4003,7 +4174,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" s="40">
         <f>IF('Adoption Model'!D10&lt;='Adoption Model'!C10, "PASS", "FAIL")</f>
@@ -4015,7 +4186,7 @@
         <f>IF('Adoption Model'!F10&lt;='Adoption Model'!E10, "PASS", "FAIL")</f>
       </c>
       <c r="F10" s="40" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G10" s="41">
         <f>IF(AND(C10="PASS", D10="PASS", E10="PASS"), "RECONCILED", "FAIL")</f>
@@ -4023,7 +4194,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="40">
         <f>IF('Adoption Model'!D11&lt;='Adoption Model'!C11, "PASS", "FAIL")</f>
@@ -4043,7 +4214,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C12" s="40">
         <f>IF('Adoption Model'!D12&lt;='Adoption Model'!C12, "PASS", "FAIL")</f>
@@ -4063,7 +4234,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C13" s="40">
         <f>IF('Adoption Model'!D13&lt;='Adoption Model'!C13, "PASS", "FAIL")</f>
@@ -4083,7 +4254,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" s="40">
         <f>IF('Adoption Model'!D14&lt;='Adoption Model'!C14, "PASS", "FAIL")</f>
@@ -4103,7 +4274,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C15" s="40">
         <f>IF('Adoption Model'!D15&lt;='Adoption Model'!C15, "PASS", "FAIL")</f>
@@ -4123,7 +4294,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C16" s="40">
         <f>IF('Adoption Model'!D16&lt;='Adoption Model'!C16, "PASS", "FAIL")</f>
@@ -4143,7 +4314,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C17" s="40">
         <f>IF('Adoption Model'!D17&lt;='Adoption Model'!C17, "PASS", "FAIL")</f>
@@ -4163,7 +4334,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -4173,7 +4344,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -4183,56 +4354,56 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="34" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="34" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F23" s="33"/>
       <c r="G23" s="33"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="43" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="F24" s="33"/>
       <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="44" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="33"/>
@@ -4276,7 +4447,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -4286,210 +4457,210 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F5" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F6" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G6" s="45" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F8" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D9" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="E9" s="45" t="s">
-        <v>233</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>225</v>
-      </c>
       <c r="G9" s="45" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="D11" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="E11" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="E11" s="45" t="s">
-        <v>233</v>
-      </c>
       <c r="F11" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G13" s="45" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="47"/>

--- a/submission/cheerio_growth_guide_financial_model.xlsx
+++ b/submission/cheerio_growth_guide_financial_model.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="274">
   <si>
     <t>Cheerio Growth Guide — Unit Economics &amp; Adoption Model</t>
   </si>
@@ -113,7 +113,7 @@
     <t>Expected-Value Basis</t>
   </si>
   <si>
-    <t>Retention revenue = Adopting Businesses × Hypothesized Retention Lift in pp × Monthly Plan ARPU.</t>
+    <t>Retention revenue = Adopting Businesses × Incremental Retained Yield % × Monthly Plan ARPU.</t>
   </si>
   <si>
     <t>No Double-Counting</t>
@@ -125,13 +125,13 @@
     <t>Illustrative Nature</t>
   </si>
   <si>
-    <t>All retention lifts (+2.0 pp baseline) represent testable hypotheses subject to 2-week baseline validation.</t>
+    <t>Incremental retained yield (2.0% baseline) represents a testable hypothesis subject to 2-week baseline validation.</t>
   </si>
   <si>
     <t>Run-Rate Annualization</t>
   </si>
   <si>
-    <t>Exit ARR (₹26,27,124) is compared against Annualized Month-12 Cost (₹14,21,016), yielding Exit Net Benefit ₹12,06,108 (45.9% margin), distinct from Year-1 in-period cash flow (+₹1,67,881 net, 11.4% margin).</t>
+    <t>Exit ARR (₹26,27,124) is compared against Annualized Month-12 Cost (₹14,21,013.43), yielding Exit Net Benefit ₹12,06,110.57 (45.9% margin), distinct from Year-1 in-period cash flow (+₹1,67,881 net, 11.4% margin).</t>
   </si>
   <si>
     <t>Hosting Cost Attribution</t>
@@ -140,6 +140,12 @@
     <t>Base model allocates full-platform cloud hosting (₹10,05,870) across all 67,058 account-months as a conservative stress test. Incremental feature-only allocation yields &gt;80% margin. Platform hosting must not be double-counted against baseline WhatsApp campaign P&amp;Ls.</t>
   </si>
   <si>
+    <t>Retention Definition</t>
+  </si>
+  <si>
+    <t>Modeled incremental accounts = Newly Activated Businesses × 2.0% incremental yield, surviving under 5.0% baseline monthly churn decay. Illustrative assumption, not an observed drop in company-wide churn from 5% to 3%.</t>
+  </si>
+  <si>
     <t>Model Assumptions &amp; Central Input Parameters</t>
   </si>
   <si>
@@ -224,13 +230,10 @@
     <t>% of activated accounts recording qualifying use within 30d</t>
   </si>
   <si>
-    <t>Hypothesized Retention Lift for Adopters</t>
-  </si>
-  <si>
-    <t>pp (monthly)</t>
-  </si>
-  <si>
-    <t>Hypothesized churn reduction for adopting businesses (+2.0 pp)</t>
+    <t>Incremental Retained-Account Yield from Newly Activated Businesses</t>
+  </si>
+  <si>
+    <t>Share of newly activated businesses contributing an incremental retained account (surviving under baseline 5% monthly decay)</t>
   </si>
   <si>
     <t>3. AI Model &amp; Token Economics</t>
@@ -284,13 +287,13 @@
     <t>Generated recommendation/response payload</t>
   </si>
   <si>
-    <t>Avg AI Interactions per Business / Mo</t>
-  </si>
-  <si>
-    <t>Calls / mo</t>
-  </si>
-  <si>
-    <t>Simulated wizard setups, FAQ queries, automation tests</t>
+    <t>AI Setup/Test Interactions per Newly Activated Business</t>
+  </si>
+  <si>
+    <t>Interactions / activation</t>
+  </si>
+  <si>
+    <t>Setup wizard and sandbox test calls per newly activated merchant during onboarding</t>
   </si>
   <si>
     <t>4. Platform Infrastructure Overhead</t>
@@ -422,7 +425,7 @@
     <t>Adopting Accounts</t>
   </si>
   <si>
-    <t>Retention Lift</t>
+    <t>Retained Yield %</t>
   </si>
   <si>
     <t>New Retained Accts</t>
@@ -476,7 +479,7 @@
     <t>Month 12 Exit Active Retained Accounts</t>
   </si>
   <si>
-    <t>Cumulative active retained customer accounts at Year 1 exit (73 accounts)</t>
+    <t>Cumulative active retained customer accounts surviving at Year 1 exit (73 accounts)</t>
   </si>
   <si>
     <t>Month 12 Exit Monthly Run Rate (MRR)</t>
@@ -494,19 +497,19 @@
     <t>Month 12 Recurring Monthly Operating Cost</t>
   </si>
   <si>
-    <t>Fixed (₹25k) + M12 Hosting (6,217 accts × ₹15 = ₹93,255) + M12 AI (₹163) = ₹1,18,418 / mo</t>
+    <t>Fixed (₹25k) + M12 Hosting (6,217 accts × ₹15 = ₹93,255) + M12 AI (₹162.79) = ₹1,18,417.79 / mo (~₹1,18,418)</t>
   </si>
   <si>
     <t>Annualized Month-12 Operating Cost</t>
   </si>
   <si>
-    <t>Month 12 Monthly Operating Cost × 12 months (Reconciles to ₹14,21,016 / yr)</t>
+    <t>Month 12 Monthly Operating Cost × 12 months (Reconciles to ₹14,21,013.43 / yr, ~₹14.21 Lakh)</t>
   </si>
   <si>
     <t>Exit Net Annualized Benefit (Run Rate)</t>
   </si>
   <si>
-    <t>Exit ARR (E28) minus Annualized Month-12 Cost (E30) = ₹12,06,108 / yr</t>
+    <t>Exit ARR (E28) minus Annualized Month-12 Cost (E30) = ₹12,06,110.57 / yr (~₹12.06 Lakh)</t>
   </si>
   <si>
     <t>Exit Annualized Contribution Margin</t>
@@ -542,16 +545,16 @@
     <t>Conversion efficiency across onboarding wizard</t>
   </si>
   <si>
-    <t>Retention Improvement (pp)</t>
-  </si>
-  <si>
-    <t>Observed drop in monthly business churn rate</t>
-  </si>
-  <si>
-    <t>Avg AI Interactions / Mo</t>
-  </si>
-  <si>
-    <t>Depth of chatbot and automation customization</t>
+    <t>Incremental Retained Yield %</t>
+  </si>
+  <si>
+    <t>Share of newly activated businesses yielding an incremental retained account</t>
+  </si>
+  <si>
+    <t>AI Setup/Test Interactions / Activation</t>
+  </si>
+  <si>
+    <t>Onboarding interactions per newly activated business</t>
   </si>
   <si>
     <t>Total 12M Activations (Est.)</t>
@@ -611,22 +614,22 @@
     <t>Exit Net Benefit / Exit ARR (45.9% Base, 77.9% Optimistic)</t>
   </si>
   <si>
-    <t>SENSITIVITY MATRIX: 12-Month Exit Annualized Net Benefit (₹) by Activation Rate &amp; Retention Lift</t>
-  </si>
-  <si>
-    <t>Activation Rate \ Retention Lift</t>
-  </si>
-  <si>
-    <t>+1.0 pp</t>
-  </si>
-  <si>
-    <t>+1.5 pp</t>
-  </si>
-  <si>
-    <t>+2.0 pp (Base)</t>
-  </si>
-  <si>
-    <t>+2.5 pp</t>
+    <t>SENSITIVITY MATRIX: 12-Month Exit Annualized Net Benefit (₹) by Activation Rate &amp; Retained Yield</t>
+  </si>
+  <si>
+    <t>Activation Rate \ Retained Yield</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>2.0% (Base)</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
   <si>
     <t>15% (Conservative)</t>
@@ -704,7 +707,7 @@
     <t>Audit Explanation &amp; Commercial Context</t>
   </si>
   <si>
-    <t>Year 1 base case absorbs ₹25,000/mo fixed overhead (₹3.00L) and ₹15/account hosting (₹10.06L) across all 5,000–6,217 accounts before cohort compounding matures. Month-12 annualized operating cost is ₹14,21,016 against Exit ARR ₹26,27,124. The 75% hurdle is achieved under Optimistic scale (77.9%), in Year 2 steady state, or under incremental feature cost attribution (&gt;80%).</t>
+    <t>Year 1 base case absorbs ₹25,000/mo fixed overhead (₹3.00L) and ₹15/account hosting (₹10.06L) across all 5,000–6,217 accounts before cohort compounding matures. Month-12 annualized operating cost is ₹14,21,013 against Exit ARR ₹26,27,124. The 75% hurdle is achieved under Optimistic scale (77.9%), in Year 2 steady state, or under incremental feature cost attribution (&gt;80%).</t>
   </si>
   <si>
     <t>Strategic justification for audit trigger</t>
@@ -740,7 +743,7 @@
     <t>USD</t>
   </si>
   <si>
-    <t>13-Oct-2026</t>
+    <t>14-Oct-2026</t>
   </si>
   <si>
     <t>Official public pay-as-you-go pricing tier ($0.15/1M input)</t>
@@ -824,19 +827,19 @@
     <t>Standard SMB SaaS benchmark prior to guided feature activation</t>
   </si>
   <si>
-    <t>Hypothesized Retention Lift</t>
-  </si>
-  <si>
-    <t>+2.0 pp (to 3.0% churn)</t>
+    <t>Incremental Retained-Account Yield</t>
+  </si>
+  <si>
+    <t>2.0% per activation</t>
   </si>
   <si>
     <t>Product Strategy Hypothesis</t>
   </si>
   <si>
-    <t>Subject to pre-rollout 2-week baseline measurement period</t>
-  </si>
-  <si>
-    <t>DISCLAIMER: This financial model is an exploratory projection created for the Cheerio AI Product Intern Assignment B take-home evaluation. Modeled retention lifts (+2.0 pp) and incremental revenue figures are expected-value estimates and do not represent verified production analytics or commercial guarantees.</t>
+    <t>2.0% of newly activated businesses yield an incremental saved account (5% monthly decay applied; not a company churn reduction from 5% to 3%)</t>
+  </si>
+  <si>
+    <t>DISCLAIMER: This financial model is an exploratory projection created for the Cheerio AI Product Intern Assignment B take-home evaluation. Modeled incremental retained yields (2.0% base) and incremental revenue figures are expected-value estimates and do not represent verified production analytics or commercial guarantees.</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1427,7 @@
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
   </sheetPr>
-  <dimension ref="B2:C26"/>
+  <dimension ref="B2:C27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1596,6 +1599,14 @@
       </c>
       <c r="C26" s="4" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1636,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -1633,7 +1644,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -1641,24 +1652,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1666,63 +1677,63 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" s="11">
         <v>5000</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="14">
         <v>0.02</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" s="15">
         <v>2999</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" s="14">
         <v>0.05</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1730,77 +1741,77 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" s="14">
         <v>0.7</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" s="14">
         <v>0.4</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="14">
         <v>0.25</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" s="14">
         <v>0.6</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16" s="14">
         <v>0.02</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1808,105 +1819,105 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="17">
         <v>0.15</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="17">
         <v>0.6</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="18">
         <v>84</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" s="11">
         <v>650</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" s="11">
         <v>250</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" s="11">
         <v>18</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -1914,30 +1925,30 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" s="18">
         <v>15</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" s="15">
         <v>25000</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +1982,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -1982,7 +1993,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -1993,33 +2004,33 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="20">
         <f>Assumptions!$C$7</f>
@@ -2042,7 +2053,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="20">
         <f>ROUND(C6 * (1 + Assumptions!$C$8), 0)</f>
@@ -2065,7 +2076,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="20">
         <f>ROUND(C7 * (1 + Assumptions!$C$8), 0)</f>
@@ -2088,7 +2099,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="20">
         <f>ROUND(C8 * (1 + Assumptions!$C$8), 0)</f>
@@ -2111,7 +2122,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="20">
         <f>ROUND(C9 * (1 + Assumptions!$C$8), 0)</f>
@@ -2134,7 +2145,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="20">
         <f>ROUND(C10 * (1 + Assumptions!$C$8), 0)</f>
@@ -2157,7 +2168,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="20">
         <f>ROUND(C11 * (1 + Assumptions!$C$8), 0)</f>
@@ -2180,7 +2191,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" s="20">
         <f>ROUND(C12 * (1 + Assumptions!$C$8), 0)</f>
@@ -2203,7 +2214,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="20">
         <f>ROUND(C13 * (1 + Assumptions!$C$8), 0)</f>
@@ -2226,7 +2237,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="20">
         <f>ROUND(C14 * (1 + Assumptions!$C$8), 0)</f>
@@ -2249,7 +2260,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="20">
         <f>ROUND(C15 * (1 + Assumptions!$C$8), 0)</f>
@@ -2272,7 +2283,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="20">
         <f>ROUND(C16 * (1 + Assumptions!$C$8), 0)</f>
@@ -2295,10 +2306,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" s="23">
         <f>AVERAGE(C6:C17)</f>
@@ -2347,7 +2358,7 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2362,7 +2373,7 @@
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2377,45 +2388,45 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="20">
         <f>'Adoption Model'!F6 * Assumptions!$C$24</f>
@@ -2450,7 +2461,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="20">
         <f>'Adoption Model'!F7 * Assumptions!$C$24</f>
@@ -2485,7 +2496,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="20">
         <f>'Adoption Model'!F8 * Assumptions!$C$24</f>
@@ -2520,7 +2531,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="20">
         <f>'Adoption Model'!F9 * Assumptions!$C$24</f>
@@ -2555,7 +2566,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="20">
         <f>'Adoption Model'!F10 * Assumptions!$C$24</f>
@@ -2590,7 +2601,7 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="20">
         <f>'Adoption Model'!F11 * Assumptions!$C$24</f>
@@ -2625,7 +2636,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="20">
         <f>'Adoption Model'!F12 * Assumptions!$C$24</f>
@@ -2660,7 +2671,7 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" s="20">
         <f>'Adoption Model'!F13 * Assumptions!$C$24</f>
@@ -2695,7 +2706,7 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="20">
         <f>'Adoption Model'!F14 * Assumptions!$C$24</f>
@@ -2730,7 +2741,7 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="20">
         <f>'Adoption Model'!F15 * Assumptions!$C$24</f>
@@ -2765,7 +2776,7 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="20">
         <f>'Adoption Model'!F16 * Assumptions!$C$24</f>
@@ -2800,7 +2811,7 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="20">
         <f>'Adoption Model'!F17 * Assumptions!$C$24</f>
@@ -2835,10 +2846,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C6:C17)</f>
@@ -2891,8 +2902,8 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
     <col min="6" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
@@ -2901,7 +2912,7 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2915,7 +2926,7 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2929,42 +2940,42 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="20">
         <f>'Adoption Model'!F6</f>
@@ -2996,7 +3007,7 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="20">
         <f>'Adoption Model'!F7</f>
@@ -3028,7 +3039,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="20">
         <f>'Adoption Model'!F8</f>
@@ -3060,7 +3071,7 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="20">
         <f>'Adoption Model'!F9</f>
@@ -3092,7 +3103,7 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="20">
         <f>'Adoption Model'!F10</f>
@@ -3124,7 +3135,7 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="20">
         <f>'Adoption Model'!F11</f>
@@ -3156,7 +3167,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="20">
         <f>'Adoption Model'!F12</f>
@@ -3188,7 +3199,7 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" s="20">
         <f>'Adoption Model'!F13</f>
@@ -3220,7 +3231,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="20">
         <f>'Adoption Model'!F14</f>
@@ -3252,7 +3263,7 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="20">
         <f>'Adoption Model'!F15</f>
@@ -3284,7 +3295,7 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="20">
         <f>'Adoption Model'!F16</f>
@@ -3316,7 +3327,7 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="20">
         <f>'Adoption Model'!F17</f>
@@ -3348,10 +3359,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C6:C17)</f>
@@ -3383,7 +3394,7 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3397,7 +3408,7 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -3406,7 +3417,7 @@
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H22" s="33"/>
       <c r="I22" s="33"/>
@@ -3415,7 +3426,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -3424,7 +3435,7 @@
       </c>
       <c r="F23" s="27"/>
       <c r="G23" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
@@ -3433,7 +3444,7 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -3442,7 +3453,7 @@
       </c>
       <c r="F24" s="27"/>
       <c r="G24" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
@@ -3451,7 +3462,7 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -3460,7 +3471,7 @@
       </c>
       <c r="F25" s="34"/>
       <c r="G25" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
@@ -3469,7 +3480,7 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
@@ -3478,7 +3489,7 @@
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
@@ -3487,7 +3498,7 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -3496,7 +3507,7 @@
       </c>
       <c r="F27" s="27"/>
       <c r="G27" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
@@ -3505,7 +3516,7 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -3514,7 +3525,7 @@
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H28" s="33"/>
       <c r="I28" s="33"/>
@@ -3523,7 +3534,7 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -3532,7 +3543,7 @@
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
@@ -3541,7 +3552,7 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -3550,7 +3561,7 @@
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
@@ -3559,7 +3570,7 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -3568,7 +3579,7 @@
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
@@ -3577,7 +3588,7 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
@@ -3586,7 +3597,7 @@
       </c>
       <c r="F32" s="34"/>
       <c r="G32" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
@@ -3653,7 +3664,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -3662,7 +3673,7 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3671,27 +3682,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C6" s="30">
         <v>0.15</v>
@@ -3703,12 +3714,12 @@
         <v>0.35</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C7" s="30">
         <v>0.01</v>
@@ -3720,12 +3731,12 @@
         <v>0.035</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" s="20">
         <v>12</v>
@@ -3737,12 +3748,12 @@
         <v>25</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9" s="20">
         <v>2815</v>
@@ -3754,12 +3765,12 @@
         <v>6572</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C10" s="25">
         <v>1306572</v>
@@ -3771,12 +3782,12 @@
         <v>1309286</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C11" s="25">
         <v>118320</v>
@@ -3788,29 +3799,29 @@
         <v>118572</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="25">
         <v>1419841</v>
       </c>
       <c r="D12" s="27">
-        <v>1421016</v>
+        <v>1421013</v>
       </c>
       <c r="E12" s="25">
         <v>1422858</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="25">
         <v>422859</v>
@@ -3822,12 +3833,12 @@
         <v>3655781</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C14" s="25">
         <v>-883713</v>
@@ -3839,12 +3850,12 @@
         <v>2346495</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C15" s="30">
         <v>-2.09</v>
@@ -3856,12 +3867,12 @@
         <v>0.642</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="25">
         <v>755748</v>
@@ -3873,29 +3884,29 @@
         <v>6441852</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="25">
         <v>-664093</v>
       </c>
       <c r="D17" s="27">
-        <v>1206108</v>
+        <v>1206111</v>
       </c>
       <c r="E17" s="25">
         <v>5018994</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C18" s="30">
         <v>-0.879</v>
@@ -3907,12 +3918,12 @@
         <v>0.779</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -3921,27 +3932,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C23" s="37">
         <v>-664484</v>
@@ -3958,7 +3969,7 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C24" s="37">
         <v>-412959</v>
@@ -3975,7 +3986,7 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C25" s="37">
         <v>-89457</v>
@@ -3984,7 +3995,7 @@
         <v>558327</v>
       </c>
       <c r="E25" s="38">
-        <v>1206108</v>
+        <v>1206111</v>
       </c>
       <c r="F25" s="39">
         <v>1853895</v>
@@ -3992,7 +4003,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C26" s="39">
         <v>126080</v>
@@ -4009,7 +4020,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C27" s="39">
         <v>449581</v>
@@ -4051,7 +4062,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -4061,7 +4072,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -4071,30 +4082,30 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="40">
         <f>IF('Adoption Model'!D6&lt;='Adoption Model'!C6, "PASS", "FAIL")</f>
@@ -4106,7 +4117,7 @@
         <f>IF('Adoption Model'!F6&lt;='Adoption Model'!E6, "PASS", "FAIL")</f>
       </c>
       <c r="F6" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G6" s="41">
         <f>IF(AND(C6="PASS", D6="PASS", E6="PASS"), "RECONCILED", "FAIL")</f>
@@ -4114,7 +4125,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="40">
         <f>IF('Adoption Model'!D7&lt;='Adoption Model'!C7, "PASS", "FAIL")</f>
@@ -4126,7 +4137,7 @@
         <f>IF('Adoption Model'!F7&lt;='Adoption Model'!E7, "PASS", "FAIL")</f>
       </c>
       <c r="F7" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G7" s="41">
         <f>IF(AND(C7="PASS", D7="PASS", E7="PASS"), "RECONCILED", "FAIL")</f>
@@ -4134,7 +4145,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="40">
         <f>IF('Adoption Model'!D8&lt;='Adoption Model'!C8, "PASS", "FAIL")</f>
@@ -4146,7 +4157,7 @@
         <f>IF('Adoption Model'!F8&lt;='Adoption Model'!E8, "PASS", "FAIL")</f>
       </c>
       <c r="F8" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G8" s="41">
         <f>IF(AND(C8="PASS", D8="PASS", E8="PASS"), "RECONCILED", "FAIL")</f>
@@ -4154,7 +4165,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="40">
         <f>IF('Adoption Model'!D9&lt;='Adoption Model'!C9, "PASS", "FAIL")</f>
@@ -4166,7 +4177,7 @@
         <f>IF('Adoption Model'!F9&lt;='Adoption Model'!E9, "PASS", "FAIL")</f>
       </c>
       <c r="F9" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G9" s="41">
         <f>IF(AND(C9="PASS", D9="PASS", E9="PASS"), "RECONCILED", "FAIL")</f>
@@ -4174,7 +4185,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="40">
         <f>IF('Adoption Model'!D10&lt;='Adoption Model'!C10, "PASS", "FAIL")</f>
@@ -4186,7 +4197,7 @@
         <f>IF('Adoption Model'!F10&lt;='Adoption Model'!E10, "PASS", "FAIL")</f>
       </c>
       <c r="F10" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G10" s="41">
         <f>IF(AND(C10="PASS", D10="PASS", E10="PASS"), "RECONCILED", "FAIL")</f>
@@ -4194,7 +4205,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="40">
         <f>IF('Adoption Model'!D11&lt;='Adoption Model'!C11, "PASS", "FAIL")</f>
@@ -4214,7 +4225,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="40">
         <f>IF('Adoption Model'!D12&lt;='Adoption Model'!C12, "PASS", "FAIL")</f>
@@ -4234,7 +4245,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" s="40">
         <f>IF('Adoption Model'!D13&lt;='Adoption Model'!C13, "PASS", "FAIL")</f>
@@ -4254,7 +4265,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="40">
         <f>IF('Adoption Model'!D14&lt;='Adoption Model'!C14, "PASS", "FAIL")</f>
@@ -4274,7 +4285,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="40">
         <f>IF('Adoption Model'!D15&lt;='Adoption Model'!C15, "PASS", "FAIL")</f>
@@ -4294,7 +4305,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="40">
         <f>IF('Adoption Model'!D16&lt;='Adoption Model'!C16, "PASS", "FAIL")</f>
@@ -4314,7 +4325,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="40">
         <f>IF('Adoption Model'!D17&lt;='Adoption Model'!C17, "PASS", "FAIL")</f>
@@ -4334,7 +4345,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -4344,7 +4355,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -4354,56 +4365,56 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="34" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F23" s="33"/>
       <c r="G23" s="33"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F24" s="33"/>
       <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="33"/>
@@ -4447,7 +4458,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -4457,210 +4468,210 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F5" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F6" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G6" s="45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F9" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G9" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G13" s="45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="47"/>
